--- a/data/tab1-zpl_09-2025.xlsx
+++ b/data/tab1-zpl_09-2025.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Образование\Магистратура\Диплом\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Образование\Магистратура\Диплом\ITMO_NIR\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F0EFC78-6CFE-4A20-AD0B-BF6072BE0C1D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A2D5993-5AAC-4B2E-B48D-79160BF028BC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1785" yWindow="7770" windowWidth="21600" windowHeight="10335" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17070" yWindow="5640" windowWidth="11790" windowHeight="11250" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -881,7 +881,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -932,6 +932,12 @@
     <xf numFmtId="1" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -953,12 +959,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -975,6 +975,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1367,134 +1376,134 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25"/>
-      <c r="O1" s="25"/>
-      <c r="P1" s="25"/>
-      <c r="Q1" s="25"/>
-      <c r="R1" s="25"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
+      <c r="O1" s="27"/>
+      <c r="P1" s="27"/>
+      <c r="Q1" s="27"/>
+      <c r="R1" s="27"/>
     </row>
     <row r="2" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="25"/>
-      <c r="O2" s="25"/>
-      <c r="P2" s="25"/>
-      <c r="Q2" s="25"/>
-      <c r="R2" s="25"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="27"/>
+      <c r="K2" s="27"/>
+      <c r="L2" s="27"/>
+      <c r="M2" s="27"/>
+      <c r="N2" s="27"/>
+      <c r="O2" s="27"/>
+      <c r="P2" s="27"/>
+      <c r="Q2" s="27"/>
+      <c r="R2" s="27"/>
     </row>
     <row r="3" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
     </row>
     <row r="4" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="26"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
     </row>
     <row r="5" spans="1:18" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="29"/>
-      <c r="B5" s="27" t="s">
+      <c r="B5" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="20" t="s">
+      <c r="C5" s="22" t="s">
         <v>2</v>
       </c>
       <c r="D5" s="31"/>
       <c r="E5" s="31"/>
       <c r="F5" s="29"/>
-      <c r="G5" s="27" t="s">
+      <c r="G5" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="H5" s="27" t="s">
+      <c r="H5" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="I5" s="27" t="s">
+      <c r="I5" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="J5" s="27" t="s">
+      <c r="J5" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="K5" s="27" t="s">
+      <c r="K5" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="L5" s="27" t="s">
+      <c r="L5" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="M5" s="27" t="s">
+      <c r="M5" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="N5" s="27" t="s">
+      <c r="N5" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="O5" s="27" t="s">
+      <c r="O5" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="P5" s="27" t="s">
+      <c r="P5" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="Q5" s="20" t="s">
+      <c r="Q5" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="R5" s="22" t="s">
+      <c r="R5" s="24" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="30"/>
-      <c r="B6" s="28"/>
+      <c r="B6" s="21"/>
       <c r="C6" s="32"/>
       <c r="D6" s="33"/>
       <c r="E6" s="33"/>
       <c r="F6" s="34"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="28"/>
-      <c r="J6" s="28"/>
-      <c r="K6" s="28"/>
-      <c r="L6" s="28"/>
-      <c r="M6" s="28"/>
-      <c r="N6" s="28"/>
-      <c r="O6" s="28"/>
-      <c r="P6" s="28"/>
-      <c r="Q6" s="21"/>
-      <c r="R6" s="23"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="21"/>
+      <c r="I6" s="21"/>
+      <c r="J6" s="21"/>
+      <c r="K6" s="21"/>
+      <c r="L6" s="21"/>
+      <c r="M6" s="21"/>
+      <c r="N6" s="21"/>
+      <c r="O6" s="21"/>
+      <c r="P6" s="21"/>
+      <c r="Q6" s="23"/>
+      <c r="R6" s="25"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="30"/>
-      <c r="B7" s="28"/>
+      <c r="B7" s="21"/>
       <c r="C7" s="5" t="s">
         <v>8</v>
       </c>
@@ -1507,18 +1516,18 @@
       <c r="F7" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="28"/>
-      <c r="H7" s="28"/>
-      <c r="I7" s="28"/>
-      <c r="J7" s="28"/>
-      <c r="K7" s="28"/>
-      <c r="L7" s="28"/>
-      <c r="M7" s="28"/>
-      <c r="N7" s="28"/>
-      <c r="O7" s="28"/>
-      <c r="P7" s="28"/>
-      <c r="Q7" s="21"/>
-      <c r="R7" s="24"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="21"/>
+      <c r="I7" s="21"/>
+      <c r="J7" s="21"/>
+      <c r="K7" s="21"/>
+      <c r="L7" s="21"/>
+      <c r="M7" s="21"/>
+      <c r="N7" s="21"/>
+      <c r="O7" s="21"/>
+      <c r="P7" s="21"/>
+      <c r="Q7" s="23"/>
+      <c r="R7" s="26"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
@@ -3466,9 +3475,15 @@
       <c r="O42" s="19">
         <v>96182</v>
       </c>
-      <c r="P42" s="16"/>
-      <c r="Q42" s="16"/>
-      <c r="R42" s="16"/>
+      <c r="P42" s="36">
+        <v>99707</v>
+      </c>
+      <c r="Q42" s="35">
+        <v>98193</v>
+      </c>
+      <c r="R42" s="37">
+        <v>139727</v>
+      </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
@@ -3499,6 +3514,8 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="H5:H7"/>
     <mergeCell ref="I5:I7"/>
     <mergeCell ref="J5:J7"/>
     <mergeCell ref="Q5:Q7"/>
@@ -3515,8 +3532,6 @@
     <mergeCell ref="P5:P7"/>
     <mergeCell ref="A5:A7"/>
     <mergeCell ref="C5:F6"/>
-    <mergeCell ref="G5:G7"/>
-    <mergeCell ref="H5:H7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="70" orientation="landscape" r:id="rId1"/>
